--- a/Result/profitability/5324.xlsx
+++ b/Result/profitability/5324.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,13 +669,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1225</v>
+        <v>0.05749999999999997</v>
       </c>
       <c r="N2" t="n">
-        <v>34.0575</v>
+        <v>35.45375</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.1</v>
       </c>
       <c r="M3" t="n">
-        <v>0.04749999999999997</v>
+        <v>-0.02750000000000003</v>
       </c>
       <c r="N3" t="n">
-        <v>27.74875</v>
+        <v>29.73249999999999</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.46</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.08250000000000003</v>
+        <v>-0.07750000000000003</v>
       </c>
       <c r="N4" t="n">
-        <v>27.2975</v>
+        <v>26.71625</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.49</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.13625</v>
+        <v>-0.1325</v>
       </c>
       <c r="N5" t="n">
-        <v>24.28</v>
+        <v>23.52875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.3</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1675</v>
+        <v>-0.145</v>
       </c>
       <c r="N6" t="n">
-        <v>21.93125</v>
+        <v>21.41625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.51</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.20625</v>
+        <v>-0.24</v>
       </c>
       <c r="N7" t="n">
-        <v>20.08375</v>
+        <v>20.56125</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,13 +1391,13 @@
         <v>-0.24</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2675000000000001</v>
+        <v>-0.25625</v>
       </c>
       <c r="N8" t="n">
-        <v>18.81125</v>
+        <v>17.25375</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1518,7 +1518,7 @@
         <v>-0.45</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3100000000000001</v>
+        <v>-0.31</v>
       </c>
       <c r="N9" t="n">
         <v>15.5975</v>
@@ -1772,7 +1772,7 @@
         <v>2.18</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.0575</v>
+        <v>-0.05750000000000005</v>
       </c>
       <c r="N11" t="n">
         <v>27.34</v>
@@ -1899,7 +1899,7 @@
         <v>0.72</v>
       </c>
       <c r="M12" t="n">
-        <v>0.09</v>
+        <v>0.08999999999999996</v>
       </c>
       <c r="N12" t="n">
         <v>30.055</v>
@@ -2026,7 +2026,7 @@
         <v>1.81</v>
       </c>
       <c r="M13" t="n">
-        <v>0.3775</v>
+        <v>0.3774999999999999</v>
       </c>
       <c r="N13" t="n">
         <v>32.5875</v>
@@ -9800,6 +9800,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5324</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>304</v>
+      </c>
+      <c r="D75" t="n">
+        <v>186</v>
+      </c>
+      <c r="E75" t="n">
+        <v>118</v>
+      </c>
+      <c r="F75" t="n">
+        <v>38.86</v>
+      </c>
+      <c r="G75" t="n">
+        <v>15</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>4.84%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-15</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.11125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>38.4075</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.8181818181818181</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-12.46</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.2427903351519876</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.6000000000000001</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-6.009999999999998</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.1339425005571651</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
